--- a/wordlist_template.xlsx
+++ b/wordlist_template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\claude\dictation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D49A311-8928-4F48-B0AB-9E640267252F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6A80750-17DB-46E3-9527-DA68D905D082}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="33120" windowHeight="18000" activeTab="5" xr2:uid="{65D37949-D610-485E-A22D-3A51B9BE5A8F}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="33120" windowHeight="18000" activeTab="1" xr2:uid="{65D37949-D610-485E-A22D-3A51B9BE5A8F}"/>
   </bookViews>
   <sheets>
     <sheet name="unit" sheetId="2" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="259" uniqueCount="189">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="166">
   <si>
     <t>uid</t>
     <phoneticPr fontId="18" type="noConversion"/>
@@ -39,10 +39,6 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>备注：311代表三年级第一学期第一单元</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>易错字</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
@@ -284,14 +280,6 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>单元表</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>课程表</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>basic_word</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
@@ -444,99 +432,19 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>写字表</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>未完待续</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>wid</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>代表3111课第01个生字</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>需要听写的字</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>第一个组词</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>第一个组词的拼音</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>第二个组词</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>第二个组词的拼音</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>lid</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>备注：lid = 3111代表第311单元第1课</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>ltitle</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <t>lname</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>课程名称</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>注：在最前方增加了一个历史上的高频易错字，作为冷启动数据源</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>课程标题</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>在显示的时候可以使用ltitle+lname的形式展示，如 “第1课 大青树下的小学”</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>高频错别字表</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>冷启动错别字</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>全部位于3000课下</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>易错字正确组词</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>易错字正确组词拼音</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>易错字易混字，如拔容易写错作拨</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>易错字易混字拼音</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
@@ -1716,7 +1624,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2606EEC2-D8F6-4998-9603-CA4879539C65}">
-  <dimension ref="A1:B12"/>
+  <dimension ref="A1:B9"/>
   <sheetFormatPr defaultRowHeight="14.15" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="10.5" customWidth="1"/>
@@ -1743,7 +1651,7 @@
         <v>312</v>
       </c>
       <c r="B3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
@@ -1751,7 +1659,7 @@
         <v>313</v>
       </c>
       <c r="B4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.35">
@@ -1759,7 +1667,7 @@
         <v>314</v>
       </c>
       <c r="B5" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.35">
@@ -1767,7 +1675,7 @@
         <v>315</v>
       </c>
       <c r="B6" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.35">
@@ -1775,7 +1683,7 @@
         <v>316</v>
       </c>
       <c r="B7" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.35">
@@ -1783,7 +1691,7 @@
         <v>317</v>
       </c>
       <c r="B8" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.35">
@@ -1791,17 +1699,7 @@
         <v>318</v>
       </c>
       <c r="B9" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A11" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A12" t="s">
-        <v>3</v>
+        <v>43</v>
       </c>
     </row>
   </sheetData>
@@ -1813,7 +1711,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F126FF78-A7FE-4F96-B0FD-A6BE376CAFDE}">
-  <dimension ref="A1:C44"/>
+  <dimension ref="A1:C37"/>
   <sheetFormatPr defaultRowHeight="14.15" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="10.35546875" customWidth="1"/>
@@ -1823,13 +1721,13 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>117</v>
+        <v>106</v>
       </c>
       <c r="B1" t="s">
-        <v>119</v>
+        <v>107</v>
       </c>
       <c r="C1" t="s">
-        <v>120</v>
+        <v>108</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
@@ -1837,10 +1735,10 @@
         <v>3000</v>
       </c>
       <c r="B2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2" t="s">
         <v>4</v>
-      </c>
-      <c r="C2" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.35">
@@ -1848,10 +1746,10 @@
         <v>3111</v>
       </c>
       <c r="B3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
@@ -1859,10 +1757,10 @@
         <v>3112</v>
       </c>
       <c r="B4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C4" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
@@ -1870,10 +1768,10 @@
         <v>3113</v>
       </c>
       <c r="B5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
@@ -1884,7 +1782,7 @@
         <v>2</v>
       </c>
       <c r="C6" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.35">
@@ -1892,10 +1790,10 @@
         <v>3121</v>
       </c>
       <c r="B7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C7" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.35">
@@ -1903,10 +1801,10 @@
         <v>3122</v>
       </c>
       <c r="B8" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C8" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.35">
@@ -1914,10 +1812,10 @@
         <v>3123</v>
       </c>
       <c r="B9" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C9" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.35">
@@ -1925,10 +1823,10 @@
         <v>3124</v>
       </c>
       <c r="B10" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C10" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.35">
@@ -1936,10 +1834,10 @@
         <v>3125</v>
       </c>
       <c r="B11" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C11" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.35">
@@ -1947,10 +1845,10 @@
         <v>3131</v>
       </c>
       <c r="B12" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C12" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.35">
@@ -1958,10 +1856,10 @@
         <v>3132</v>
       </c>
       <c r="B13" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C13" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.35">
@@ -1969,10 +1867,10 @@
         <v>3133</v>
       </c>
       <c r="B14" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C14" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.35">
@@ -1980,10 +1878,10 @@
         <v>3134</v>
       </c>
       <c r="B15" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C15" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.35">
@@ -1991,10 +1889,10 @@
         <v>3135</v>
       </c>
       <c r="B16" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C16" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.35">
@@ -2002,10 +1900,10 @@
         <v>3141</v>
       </c>
       <c r="B17" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C17" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.35">
@@ -2013,10 +1911,10 @@
         <v>3142</v>
       </c>
       <c r="B18" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C18" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.35">
@@ -2024,10 +1922,10 @@
         <v>3143</v>
       </c>
       <c r="B19" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C19" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.35">
@@ -2035,10 +1933,10 @@
         <v>3144</v>
       </c>
       <c r="B20" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C20" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.35">
@@ -2046,10 +1944,10 @@
         <v>3151</v>
       </c>
       <c r="B21" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C21" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.35">
@@ -2057,10 +1955,10 @@
         <v>3152</v>
       </c>
       <c r="B22" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C22" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.35">
@@ -2068,10 +1966,10 @@
         <v>3153</v>
       </c>
       <c r="B23" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C23" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.35">
@@ -2079,10 +1977,10 @@
         <v>3161</v>
       </c>
       <c r="B24" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C24" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.35">
@@ -2090,10 +1988,10 @@
         <v>3162</v>
       </c>
       <c r="B25" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C25" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.35">
@@ -2101,10 +1999,10 @@
         <v>3163</v>
       </c>
       <c r="B26" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C26" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.35">
@@ -2112,10 +2010,10 @@
         <v>3164</v>
       </c>
       <c r="B27" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C27" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.35">
@@ -2123,10 +2021,10 @@
         <v>3165</v>
       </c>
       <c r="B28" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C28" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.35">
@@ -2134,10 +2032,10 @@
         <v>3171</v>
       </c>
       <c r="B29" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C29" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.35">
@@ -2145,10 +2043,10 @@
         <v>3172</v>
       </c>
       <c r="B30" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C30" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.35">
@@ -2156,10 +2054,10 @@
         <v>3173</v>
       </c>
       <c r="B31" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C31" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.35">
@@ -2167,10 +2065,10 @@
         <v>3174</v>
       </c>
       <c r="B32" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C32" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.35">
@@ -2178,10 +2076,10 @@
         <v>3181</v>
       </c>
       <c r="B33" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C33" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.35">
@@ -2189,10 +2087,10 @@
         <v>3182</v>
       </c>
       <c r="B34" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C34" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.35">
@@ -2200,10 +2098,10 @@
         <v>3183</v>
       </c>
       <c r="B35" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C35" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.35">
@@ -2211,10 +2109,10 @@
         <v>3184</v>
       </c>
       <c r="B36" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C36" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.35">
@@ -2222,44 +2120,10 @@
         <v>3185</v>
       </c>
       <c r="B37" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C37" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A40" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A41" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A42" t="s">
-        <v>119</v>
-      </c>
-      <c r="B42" t="s">
-        <v>123</v>
-      </c>
-      <c r="C42" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A43" t="s">
-        <v>120</v>
-      </c>
-      <c r="B43" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A44" t="s">
-        <v>124</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -2271,7 +2135,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EAFD25AA-A680-413B-908E-EA248C8F5892}">
-  <dimension ref="A1:F46"/>
+  <dimension ref="A1:F16"/>
   <sheetFormatPr defaultRowHeight="14.15" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="10.35546875" customWidth="1"/>
@@ -2279,22 +2143,22 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="B1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C1" t="s">
         <v>70</v>
       </c>
-      <c r="C1" t="s">
-        <v>73</v>
-      </c>
       <c r="D1" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="E1" t="s">
+        <v>71</v>
+      </c>
+      <c r="F1" t="s">
         <v>74</v>
-      </c>
-      <c r="F1" t="s">
-        <v>77</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.35">
@@ -2302,13 +2166,13 @@
         <v>311101</v>
       </c>
       <c r="B2" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="C2" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="E2" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.35">
@@ -2316,13 +2180,13 @@
         <v>311102</v>
       </c>
       <c r="B3" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="C3" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="E3" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.35">
@@ -2330,13 +2194,13 @@
         <v>311103</v>
       </c>
       <c r="B4" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="C4" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="E4" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.35">
@@ -2344,10 +2208,10 @@
         <v>311104</v>
       </c>
       <c r="B5" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="C5" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.35">
@@ -2355,10 +2219,10 @@
         <v>311105</v>
       </c>
       <c r="B6" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="C6" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.35">
@@ -2366,7 +2230,7 @@
         <v>311106</v>
       </c>
       <c r="B7" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.35">
@@ -2374,7 +2238,7 @@
         <v>311107</v>
       </c>
       <c r="B8" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.35">
@@ -2382,7 +2246,7 @@
         <v>311108</v>
       </c>
       <c r="B9" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.35">
@@ -2390,7 +2254,7 @@
         <v>311109</v>
       </c>
       <c r="B10" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.35">
@@ -2398,7 +2262,7 @@
         <v>311110</v>
       </c>
       <c r="B11" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.35">
@@ -2406,7 +2270,7 @@
         <v>311111</v>
       </c>
       <c r="B12" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.35">
@@ -2414,7 +2278,7 @@
         <v>311112</v>
       </c>
       <c r="B13" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.35">
@@ -2422,7 +2286,7 @@
         <v>311113</v>
       </c>
       <c r="B14" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.35">
@@ -2430,7 +2294,7 @@
         <v>311201</v>
       </c>
       <c r="B15" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.35">
@@ -2438,68 +2302,7 @@
         <v>311202</v>
       </c>
       <c r="B16" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A39" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A40" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A41" t="s">
-        <v>110</v>
-      </c>
-      <c r="B41">
-        <v>311101</v>
-      </c>
-      <c r="C41" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A42" t="s">
-        <v>70</v>
-      </c>
-      <c r="B42" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A43" t="s">
-        <v>73</v>
-      </c>
-      <c r="B43" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A44" t="s">
-        <v>75</v>
-      </c>
-      <c r="B44" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A45" t="s">
-        <v>74</v>
-      </c>
-      <c r="B45" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A46" t="s">
-        <v>77</v>
-      </c>
-      <c r="B46" t="s">
-        <v>116</v>
+        <v>94</v>
       </c>
     </row>
   </sheetData>
@@ -2511,27 +2314,27 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{03138E4B-82A3-4560-8852-7BE28D232565}">
-  <dimension ref="A1:F47"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr defaultRowHeight="14.15" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
+        <v>96</v>
+      </c>
+      <c r="B1" t="s">
+        <v>97</v>
+      </c>
+      <c r="C1" t="s">
+        <v>98</v>
+      </c>
+      <c r="D1" t="s">
         <v>99</v>
       </c>
-      <c r="B1" t="s">
+      <c r="E1" t="s">
         <v>100</v>
       </c>
-      <c r="C1" t="s">
+      <c r="F1" t="s">
         <v>101</v>
-      </c>
-      <c r="D1" t="s">
-        <v>102</v>
-      </c>
-      <c r="E1" t="s">
-        <v>103</v>
-      </c>
-      <c r="F1" t="s">
-        <v>104</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.35">
@@ -2539,68 +2342,13 @@
         <v>300001</v>
       </c>
       <c r="B2" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C2" t="s">
-        <v>132</v>
+        <v>109</v>
       </c>
       <c r="E2" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A40" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A41" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A42" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A43" t="s">
-        <v>100</v>
-      </c>
-      <c r="B43" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A44" t="s">
-        <v>101</v>
-      </c>
-      <c r="B44" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A45" t="s">
-        <v>102</v>
-      </c>
-      <c r="B45" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A46" t="s">
-        <v>103</v>
-      </c>
-      <c r="B46" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A47" t="s">
-        <v>104</v>
-      </c>
-      <c r="B47" t="s">
-        <v>131</v>
+        <v>110</v>
       </c>
     </row>
   </sheetData>
@@ -2617,19 +2365,19 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>134</v>
+        <v>111</v>
       </c>
       <c r="B1" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="C1" t="s">
-        <v>176</v>
+        <v>153</v>
       </c>
       <c r="D1" t="s">
-        <v>177</v>
+        <v>154</v>
       </c>
       <c r="E1" t="s">
-        <v>178</v>
+        <v>155</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.35">
@@ -2637,10 +2385,10 @@
         <v>300081</v>
       </c>
       <c r="B2" t="s">
-        <v>186</v>
+        <v>163</v>
       </c>
       <c r="D2" t="s">
-        <v>187</v>
+        <v>164</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.35">
@@ -2648,10 +2396,10 @@
         <v>300081</v>
       </c>
       <c r="B3" t="s">
-        <v>186</v>
+        <v>163</v>
       </c>
       <c r="D3" t="s">
-        <v>188</v>
+        <v>165</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.35">
@@ -2659,10 +2407,10 @@
         <v>311181</v>
       </c>
       <c r="B4" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="D4" t="s">
-        <v>179</v>
+        <v>156</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.35">
@@ -2670,10 +2418,10 @@
         <v>311181</v>
       </c>
       <c r="B5" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="D5" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.35">
@@ -2681,10 +2429,10 @@
         <v>311182</v>
       </c>
       <c r="B6" t="s">
-        <v>180</v>
+        <v>157</v>
       </c>
       <c r="D6" t="s">
-        <v>181</v>
+        <v>158</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.35">
@@ -2692,10 +2440,10 @@
         <v>311182</v>
       </c>
       <c r="B7" t="s">
-        <v>180</v>
+        <v>157</v>
       </c>
       <c r="D7" t="s">
-        <v>182</v>
+        <v>159</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.35">
@@ -2703,10 +2451,10 @@
         <v>311183</v>
       </c>
       <c r="B8" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="D8" t="s">
-        <v>183</v>
+        <v>160</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.35">
@@ -2714,10 +2462,10 @@
         <v>311183</v>
       </c>
       <c r="B9" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="D9" t="s">
-        <v>184</v>
+        <v>161</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.35">
@@ -2725,10 +2473,10 @@
         <v>311183</v>
       </c>
       <c r="B10" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="D10" t="s">
-        <v>185</v>
+        <v>162</v>
       </c>
     </row>
   </sheetData>
@@ -2750,16 +2498,16 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>135</v>
+        <v>112</v>
       </c>
       <c r="B1" t="s">
-        <v>136</v>
+        <v>113</v>
       </c>
       <c r="C1" t="s">
-        <v>137</v>
+        <v>114</v>
       </c>
       <c r="D1" t="s">
-        <v>138</v>
+        <v>115</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.35">
@@ -2767,10 +2515,10 @@
         <v>311151</v>
       </c>
       <c r="B2" t="s">
-        <v>148</v>
+        <v>125</v>
       </c>
       <c r="C2" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.35">
@@ -2778,10 +2526,10 @@
         <v>311152</v>
       </c>
       <c r="B3" t="s">
-        <v>148</v>
+        <v>125</v>
       </c>
       <c r="C3" t="s">
-        <v>149</v>
+        <v>126</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.35">
@@ -2789,10 +2537,10 @@
         <v>311153</v>
       </c>
       <c r="B4" t="s">
-        <v>148</v>
+        <v>125</v>
       </c>
       <c r="C4" t="s">
-        <v>150</v>
+        <v>127</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.35">
@@ -2800,10 +2548,10 @@
         <v>311154</v>
       </c>
       <c r="B5" t="s">
-        <v>148</v>
+        <v>125</v>
       </c>
       <c r="C5" t="s">
-        <v>151</v>
+        <v>128</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.35">
@@ -2811,10 +2559,10 @@
         <v>311155</v>
       </c>
       <c r="B6" t="s">
-        <v>148</v>
+        <v>125</v>
       </c>
       <c r="C6" t="s">
-        <v>152</v>
+        <v>129</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.35">
@@ -2822,10 +2570,10 @@
         <v>311156</v>
       </c>
       <c r="B7" t="s">
-        <v>148</v>
+        <v>125</v>
       </c>
       <c r="C7" t="s">
-        <v>153</v>
+        <v>130</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.35">
@@ -2833,10 +2581,10 @@
         <v>311157</v>
       </c>
       <c r="B8" t="s">
-        <v>148</v>
+        <v>125</v>
       </c>
       <c r="C8" t="s">
-        <v>154</v>
+        <v>131</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.35">
@@ -2844,10 +2592,10 @@
         <v>311158</v>
       </c>
       <c r="B9" t="s">
-        <v>148</v>
+        <v>125</v>
       </c>
       <c r="C9" t="s">
-        <v>155</v>
+        <v>132</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.35">
@@ -2855,10 +2603,10 @@
         <v>311159</v>
       </c>
       <c r="B10" t="s">
-        <v>148</v>
+        <v>125</v>
       </c>
       <c r="C10" t="s">
-        <v>156</v>
+        <v>133</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.35">
@@ -2866,10 +2614,10 @@
         <v>311160</v>
       </c>
       <c r="B11" t="s">
-        <v>148</v>
+        <v>125</v>
       </c>
       <c r="C11" t="s">
-        <v>157</v>
+        <v>134</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.35">
@@ -2877,10 +2625,10 @@
         <v>311161</v>
       </c>
       <c r="B12" t="s">
-        <v>148</v>
+        <v>125</v>
       </c>
       <c r="C12" t="s">
-        <v>158</v>
+        <v>135</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.35">
@@ -2888,10 +2636,10 @@
         <v>311162</v>
       </c>
       <c r="B13" t="s">
-        <v>148</v>
+        <v>125</v>
       </c>
       <c r="C13" t="s">
-        <v>159</v>
+        <v>136</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.35">
@@ -2899,10 +2647,10 @@
         <v>311163</v>
       </c>
       <c r="B14" t="s">
-        <v>148</v>
+        <v>125</v>
       </c>
       <c r="C14" t="s">
-        <v>160</v>
+        <v>137</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.35">
@@ -2910,10 +2658,10 @@
         <v>311164</v>
       </c>
       <c r="B15" t="s">
-        <v>148</v>
+        <v>125</v>
       </c>
       <c r="C15" t="s">
-        <v>161</v>
+        <v>138</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.35">
@@ -2921,10 +2669,10 @@
         <v>311165</v>
       </c>
       <c r="B16" t="s">
-        <v>148</v>
+        <v>125</v>
       </c>
       <c r="C16" t="s">
-        <v>162</v>
+        <v>139</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.35">
@@ -2932,10 +2680,10 @@
         <v>311166</v>
       </c>
       <c r="B17" t="s">
-        <v>148</v>
+        <v>125</v>
       </c>
       <c r="C17" t="s">
-        <v>163</v>
+        <v>140</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.35">
@@ -2943,10 +2691,10 @@
         <v>311251</v>
       </c>
       <c r="B18" t="s">
-        <v>148</v>
+        <v>125</v>
       </c>
       <c r="C18" t="s">
-        <v>164</v>
+        <v>141</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.35">
@@ -2954,10 +2702,10 @@
         <v>311252</v>
       </c>
       <c r="B19" t="s">
-        <v>148</v>
+        <v>125</v>
       </c>
       <c r="C19" t="s">
-        <v>165</v>
+        <v>142</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.35">
@@ -2965,10 +2713,10 @@
         <v>311253</v>
       </c>
       <c r="B20" t="s">
-        <v>148</v>
+        <v>125</v>
       </c>
       <c r="C20" t="s">
-        <v>166</v>
+        <v>143</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.35">
@@ -2976,10 +2724,10 @@
         <v>311254</v>
       </c>
       <c r="B21" t="s">
-        <v>148</v>
+        <v>125</v>
       </c>
       <c r="C21" t="s">
-        <v>167</v>
+        <v>144</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.35">
@@ -2987,10 +2735,10 @@
         <v>311255</v>
       </c>
       <c r="B22" t="s">
-        <v>148</v>
+        <v>125</v>
       </c>
       <c r="C22" t="s">
-        <v>168</v>
+        <v>145</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.35">
@@ -2998,10 +2746,10 @@
         <v>311256</v>
       </c>
       <c r="B23" t="s">
-        <v>148</v>
+        <v>125</v>
       </c>
       <c r="C23" t="s">
-        <v>169</v>
+        <v>146</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.35">
@@ -3009,10 +2757,10 @@
         <v>311257</v>
       </c>
       <c r="B24" t="s">
-        <v>148</v>
+        <v>125</v>
       </c>
       <c r="C24" t="s">
-        <v>170</v>
+        <v>147</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.35">
@@ -3020,10 +2768,10 @@
         <v>311258</v>
       </c>
       <c r="B25" t="s">
+        <v>125</v>
+      </c>
+      <c r="C25" t="s">
         <v>148</v>
-      </c>
-      <c r="C25" t="s">
-        <v>171</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.35">
@@ -3031,10 +2779,10 @@
         <v>311259</v>
       </c>
       <c r="B26" t="s">
-        <v>148</v>
+        <v>125</v>
       </c>
       <c r="C26" t="s">
-        <v>172</v>
+        <v>149</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.35">
@@ -3042,10 +2790,10 @@
         <v>311260</v>
       </c>
       <c r="B27" t="s">
-        <v>148</v>
+        <v>125</v>
       </c>
       <c r="C27" t="s">
-        <v>173</v>
+        <v>150</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.35">
@@ -3053,10 +2801,10 @@
         <v>311261</v>
       </c>
       <c r="B28" t="s">
-        <v>148</v>
+        <v>125</v>
       </c>
       <c r="C28" t="s">
-        <v>174</v>
+        <v>151</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.35">
@@ -3064,10 +2812,10 @@
         <v>311262</v>
       </c>
       <c r="B29" t="s">
-        <v>148</v>
+        <v>125</v>
       </c>
       <c r="C29" t="s">
-        <v>175</v>
+        <v>152</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.35">
@@ -3075,10 +2823,10 @@
         <v>311451</v>
       </c>
       <c r="B30" t="s">
-        <v>139</v>
+        <v>116</v>
       </c>
       <c r="C30" t="s">
-        <v>140</v>
+        <v>117</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.35">
@@ -3086,10 +2834,10 @@
         <v>311451</v>
       </c>
       <c r="B31" t="s">
-        <v>139</v>
+        <v>116</v>
       </c>
       <c r="C31" t="s">
-        <v>141</v>
+        <v>118</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.35">
@@ -3097,10 +2845,10 @@
         <v>311451</v>
       </c>
       <c r="B32" t="s">
-        <v>139</v>
+        <v>116</v>
       </c>
       <c r="C32" t="s">
-        <v>142</v>
+        <v>119</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.35">
@@ -3108,10 +2856,10 @@
         <v>311451</v>
       </c>
       <c r="B33" t="s">
-        <v>139</v>
+        <v>116</v>
       </c>
       <c r="C33" t="s">
-        <v>143</v>
+        <v>120</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.35">
@@ -3119,10 +2867,10 @@
         <v>311451</v>
       </c>
       <c r="B34" t="s">
-        <v>139</v>
+        <v>116</v>
       </c>
       <c r="C34" t="s">
-        <v>144</v>
+        <v>121</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.35">
@@ -3130,10 +2878,10 @@
         <v>311451</v>
       </c>
       <c r="B35" t="s">
-        <v>139</v>
+        <v>116</v>
       </c>
       <c r="C35" t="s">
-        <v>145</v>
+        <v>122</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.35">
@@ -3141,10 +2889,10 @@
         <v>311451</v>
       </c>
       <c r="B36" t="s">
-        <v>139</v>
+        <v>116</v>
       </c>
       <c r="C36" t="s">
-        <v>146</v>
+        <v>123</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.35">
@@ -3152,10 +2900,10 @@
         <v>311451</v>
       </c>
       <c r="B37" t="s">
-        <v>139</v>
+        <v>116</v>
       </c>
       <c r="C37" t="s">
-        <v>147</v>
+        <v>124</v>
       </c>
     </row>
   </sheetData>

--- a/wordlist_template.xlsx
+++ b/wordlist_template.xlsx
@@ -1140,7 +1140,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C36"/>
+  <dimension ref="A1:C44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.15"/>
   <cols>
     <col width="10.35546875" customWidth="1" style="1" min="1" max="1"/>
@@ -1687,6 +1687,126 @@
       <c r="C36" s="0" t="inlineStr">
         <is>
           <t>语文园地八</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>3110</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>第一单元</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>单元复习</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>3120</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>第二单元</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>单元复习</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>3130</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>第三单元</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>单元复习</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>3140</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>第四单元</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>单元复习</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>3150</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>第五单元</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>单元复习</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>3160</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>第六单元</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>单元复习</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>3170</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>第七单元</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>单元复习</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>3180</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>第八单元</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>单元复习</t>
         </is>
       </c>
     </row>
@@ -5224,7 +5344,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.15"/>
   <sheetData>
     <row r="1">
@@ -5260,22 +5380,1322 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="0" t="n">
-        <v>300001</v>
-      </c>
-      <c r="B2" s="0" t="inlineStr">
-        <is>
-          <t>拔</t>
-        </is>
-      </c>
-      <c r="C2" s="0" t="inlineStr">
-        <is>
-          <t>海拔</t>
-        </is>
-      </c>
-      <c r="E2" s="0" t="inlineStr">
-        <is>
-          <t>点拨</t>
+      <c r="A2" t="n">
+        <v>311001</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>飘</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>飘扬</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>piāo yáng</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>漂流</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>piāo liú</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>311002</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>壮</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>强壮</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>qiáng zhuàng</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>状态</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>zhuàng tài</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>311003</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>湿</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>湿润</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>shī rùn</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>温度</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>wēn dù</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>311004</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>粗</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>粗细</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>cū xì</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>姐妹</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>jiě mèi</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>311005</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>扬</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>飞扬</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>fēi yáng</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>杨树</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>yáng shù</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>311006</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>笛</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>笛子</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>dí zi</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>禾苗</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>hé miáo</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>311007</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>互</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>互相</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>hù xiāng</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>瓦片</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>wǎ piàn</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>311008</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>狂</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>疯狂</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>fēng kuáng</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>兴旺</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>xīng wàng</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>311009</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>坡</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>山坡</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>shān pō</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>水波</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>shuǐ bō</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>311010</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>洁</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>洁白</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>jié bái</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>结束</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>jié shù</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>312001</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>径</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>石径</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>shí jìng</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>经常</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>jīng cháng</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>312002</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>未</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>未来</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>wèi lái</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>末尾</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>mò wěi</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>312003</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>朗</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>晴朗</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>qíng lǎng</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>新郎</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>xīn láng</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>312004</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>列</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>排列</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>pái liè</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>例题</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>lì tí</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>312005</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>勾</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>勾住</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>gōu zhù</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>铁勺</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>tiě sháo</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>313001</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>晒</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>风吹日晒</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>fēng chuī rì shài</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>洒水</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>sǎ shuǐ</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>313002</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>萌</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>萌发</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>méng fā</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>葫芦</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>hú lu</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>313003</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>培</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>培养</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>péi yǎng</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>陪伴</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>péi bàn</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>314001</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>宫</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>龙宫</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>lóng gōng</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>做官</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>zuò guān</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>314002</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>旅</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>旅行</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>lǚ xíng</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>民族</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>mín zú</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>314003</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>睛</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>画龙点睛</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>huà lóng diǎn jīng</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>晴天</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>qíng tiān</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>315001</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>搭</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>搭船</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>dā chuán</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>宝塔</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>bǎo tǎ</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>315002</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>耍</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>玩耍</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>wán shuǎ</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>重要</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>zhòng yào</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>315003</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>披</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>披风</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>pī fēng</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>山坡</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>shān pō</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>315004</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>拢</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>合拢</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>hé lǒng</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>打扰</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>dǎ rǎo</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>316001</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>密</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>严密</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>yán mì</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>奥秘</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>ào mì</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>316002</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>苍</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>苍翠</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>cāng cuì</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>仓库</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>cāng kù</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>316003</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>滨</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>海滨</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>hǎi bīn</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>缤纷</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>bīn fēn</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>316004</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>渔</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>渔船</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>yú chuán</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>金鱼</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>jīn yú</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>316005</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>亚</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>亚军</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>yà jūn</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>事业</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>shì yè</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>316006</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>严</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>严实</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>yán shí</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>特产</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>tè chǎn</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>316007</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>挡</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>挡住</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>dǎng zhù</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>文档</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>wén dàng</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>316008</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>材</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>木材</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>mù cái</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>财富</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>cái fù</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>317001</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>妙</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>奇妙</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>qí miào</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>抄写</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>chāo xiě</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>317002</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>秘</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>奥秘</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>ào mì</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>严密</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>yán mì</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>317003</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>部</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>部分</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>bù fen</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>陪伴</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>péi bàn</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>317004</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>姿</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>姿态</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>zī tài</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>资金</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>zī jīn</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>318001</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>棒</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>木棒</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>mù bàng</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>捧场</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>pěng chǎng</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>318002</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>考</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>考试</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>kǎo shì</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>老师</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>lǎo shī</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>318003</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>登</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>登山</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>dēng shān</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>瞪眼</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>dèng yǎn</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>318004</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>努</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>努力</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>nǔ lì</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>愤怒</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>fèn nù</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>318005</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>匆</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>匆匆</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>cōng cōng</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>切勿</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>qiè wù</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>318006</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>血</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>血液</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>xuè yè</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>器皿</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>qì mǐn</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>318007</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>呆</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>发呆</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>fā dāi</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>吊灯</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>diào dēng</t>
         </is>
       </c>
     </row>
@@ -5322,1342 +6742,1342 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
+      <c r="A2" s="0" t="n">
         <v>311281</v>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="0" t="inlineStr">
         <is>
           <t>假</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" s="0" t="inlineStr">
         <is>
           <t>jià</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D2" s="0" t="inlineStr">
         <is>
           <t>放假</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E2" s="0" t="inlineStr">
         <is>
           <t>fàng jià</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="n">
+      <c r="A3" s="0" t="n">
         <v>311281</v>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="0" t="inlineStr">
         <is>
           <t>假</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="0" t="inlineStr">
         <is>
           <t>jiǎ</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D3" s="0" t="inlineStr">
         <is>
           <t>真假</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E3" s="0" t="inlineStr">
         <is>
           <t>zhēn jiǎ</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="n">
+      <c r="A4" s="0" t="n">
         <v>312181</v>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="0" t="inlineStr">
         <is>
           <t>磨</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C4" s="0" t="inlineStr">
         <is>
           <t>mó</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D4" s="0" t="inlineStr">
         <is>
           <t>磨蹭</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E4" s="0" t="inlineStr">
         <is>
           <t>mó ceng</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="n">
+      <c r="A5" s="0" t="n">
         <v>312181</v>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="0" t="inlineStr">
         <is>
           <t>磨</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C5" s="0" t="inlineStr">
         <is>
           <t>mò</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D5" s="0" t="inlineStr">
         <is>
           <t>石磨</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E5" s="0" t="inlineStr">
         <is>
           <t>shí mò</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="n">
+      <c r="A6" s="0" t="n">
         <v>312182</v>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" s="0" t="inlineStr">
         <is>
           <t>挑</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C6" s="0" t="inlineStr">
         <is>
           <t>tiǎo</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D6" s="0" t="inlineStr">
         <is>
           <t>挑战</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E6" s="0" t="inlineStr">
         <is>
           <t>tiǎo zhàn</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="n">
+      <c r="A7" s="0" t="n">
         <v>312182</v>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B7" s="0" t="inlineStr">
         <is>
           <t>挑</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C7" s="0" t="inlineStr">
         <is>
           <t>tiāo</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D7" s="0" t="inlineStr">
         <is>
           <t>挑选</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E7" s="0" t="inlineStr">
         <is>
           <t>tiāo xuǎn</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="n">
+      <c r="A8" s="0" t="n">
         <v>313281</v>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B8" s="0" t="inlineStr">
         <is>
           <t>几</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C8" s="0" t="inlineStr">
         <is>
           <t>jī</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D8" s="0" t="inlineStr">
         <is>
           <t>几乎</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E8" s="0" t="inlineStr">
         <is>
           <t>jī hū</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="n">
+      <c r="A9" s="0" t="n">
         <v>313281</v>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B9" s="0" t="inlineStr">
         <is>
           <t>几</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C9" s="0" t="inlineStr">
         <is>
           <t>jǐ</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D9" s="0" t="inlineStr">
         <is>
           <t>几个</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E9" s="0" t="inlineStr">
         <is>
           <t>jǐ gè</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="n">
+      <c r="A10" s="0" t="n">
         <v>313381</v>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B10" s="0" t="inlineStr">
         <is>
           <t>吗</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C10" s="0" t="inlineStr">
         <is>
           <t>má</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D10" s="0" t="inlineStr">
         <is>
           <t>干吗</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E10" s="0" t="inlineStr">
         <is>
           <t>gàn má</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="n">
+      <c r="A11" s="0" t="n">
         <v>313381</v>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B11" s="0" t="inlineStr">
         <is>
           <t>吗</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C11" s="0" t="inlineStr">
         <is>
           <t>ma</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D11" s="0" t="inlineStr">
         <is>
           <t>好吗</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E11" s="0" t="inlineStr">
         <is>
           <t>hǎo ma</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="n">
+      <c r="A12" s="0" t="n">
         <v>313382</v>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B12" s="0" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C12" s="0" t="inlineStr">
         <is>
           <t>zhòng</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D12" s="0" t="inlineStr">
         <is>
           <t>中奖</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E12" s="0" t="inlineStr">
         <is>
           <t>zhòng jiǎng</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="n">
+      <c r="A13" s="0" t="n">
         <v>313382</v>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B13" s="0" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C13" s="0" t="inlineStr">
         <is>
           <t>zhōng</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D13" s="0" t="inlineStr">
         <is>
           <t>中间</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="E13" s="0" t="inlineStr">
         <is>
           <t>zhōng jiān</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="n">
+      <c r="A14" s="0" t="n">
         <v>313383</v>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B14" s="0" t="inlineStr">
         <is>
           <t>弹</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C14" s="0" t="inlineStr">
         <is>
           <t>dàn</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="D14" s="0" t="inlineStr">
         <is>
           <t>子弹</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="E14" s="0" t="inlineStr">
         <is>
           <t>zǐ dàn</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="n">
+      <c r="A15" s="0" t="n">
         <v>313383</v>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B15" s="0" t="inlineStr">
         <is>
           <t>弹</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C15" s="0" t="inlineStr">
         <is>
           <t>tán</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="D15" s="0" t="inlineStr">
         <is>
           <t>弹琴</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="E15" s="0" t="inlineStr">
         <is>
           <t>tán qín</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="n">
+      <c r="A16" s="0" t="n">
         <v>314181</v>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B16" s="0" t="inlineStr">
         <is>
           <t>少</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C16" s="0" t="inlineStr">
         <is>
           <t>shào</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="D16" s="0" t="inlineStr">
         <is>
           <t>少年</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="E16" s="0" t="inlineStr">
         <is>
           <t>shào nián</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="n">
+      <c r="A17" s="0" t="n">
         <v>314181</v>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B17" s="0" t="inlineStr">
         <is>
           <t>少</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C17" s="0" t="inlineStr">
         <is>
           <t>shǎo</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="D17" s="0" t="inlineStr">
         <is>
           <t>多少</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="E17" s="0" t="inlineStr">
         <is>
           <t>duō shao</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="n">
+      <c r="A18" s="0" t="n">
         <v>314182</v>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B18" s="0" t="inlineStr">
         <is>
           <t>冲</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="C18" s="0" t="inlineStr">
         <is>
           <t>chòng</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="D18" s="0" t="inlineStr">
         <is>
           <t>冲着</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="E18" s="0" t="inlineStr">
         <is>
           <t>chòng zhe</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="n">
+      <c r="A19" s="0" t="n">
         <v>314182</v>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B19" s="0" t="inlineStr">
         <is>
           <t>冲</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="C19" s="0" t="inlineStr">
         <is>
           <t>chōng</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="D19" s="0" t="inlineStr">
         <is>
           <t>冲击</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="E19" s="0" t="inlineStr">
         <is>
           <t>chōng jī</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="n">
+      <c r="A20" s="0" t="n">
         <v>314183</v>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B20" s="0" t="inlineStr">
         <is>
           <t>系</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="C20" s="0" t="inlineStr">
         <is>
           <t>xì</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
+      <c r="D20" s="0" t="inlineStr">
         <is>
           <t>联系</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="E20" s="0" t="inlineStr">
         <is>
           <t>lián xì</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="n">
+      <c r="A21" s="0" t="n">
         <v>314183</v>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B21" s="0" t="inlineStr">
         <is>
           <t>系</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="C21" s="0" t="inlineStr">
         <is>
           <t>jì</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
+      <c r="D21" s="0" t="inlineStr">
         <is>
           <t>系鞋带</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="E21" s="0" t="inlineStr">
         <is>
           <t>jì xié dài</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="n">
+      <c r="A22" s="0" t="n">
         <v>314281</v>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B22" s="0" t="inlineStr">
         <is>
           <t>答</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="C22" s="0" t="inlineStr">
         <is>
           <t>dā</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
+      <c r="D22" s="0" t="inlineStr">
         <is>
           <t>答应</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="E22" s="0" t="inlineStr">
         <is>
           <t>dā ying</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="n">
+      <c r="A23" s="0" t="n">
         <v>314281</v>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B23" s="0" t="inlineStr">
         <is>
           <t>答</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="C23" s="0" t="inlineStr">
         <is>
           <t>dá</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
+      <c r="D23" s="0" t="inlineStr">
         <is>
           <t>回答</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="E23" s="0" t="inlineStr">
         <is>
           <t>huí dá</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="n">
+      <c r="A24" s="0" t="n">
         <v>314282</v>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B24" s="0" t="inlineStr">
         <is>
           <t>应</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="C24" s="0" t="inlineStr">
         <is>
           <t>yìng</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
+      <c r="D24" s="0" t="inlineStr">
         <is>
           <t>呼应</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="E24" s="0" t="inlineStr">
         <is>
           <t>hū yìng</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="n">
+      <c r="A25" s="0" t="n">
         <v>314282</v>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B25" s="0" t="inlineStr">
         <is>
           <t>应</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="C25" s="0" t="inlineStr">
         <is>
           <t>yīng</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
+      <c r="D25" s="0" t="inlineStr">
         <is>
           <t>应当</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
+      <c r="E25" s="0" t="inlineStr">
         <is>
           <t>yīng dāng</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="n">
+      <c r="A26" s="0" t="n">
         <v>314381</v>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B26" s="0" t="inlineStr">
         <is>
           <t>骨</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
+      <c r="C26" s="0" t="inlineStr">
         <is>
           <t>gū</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
+      <c r="D26" s="0" t="inlineStr">
         <is>
           <t>骨碌碌</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
+      <c r="E26" s="0" t="inlineStr">
         <is>
           <t>gū lu lu</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="n">
+      <c r="A27" s="0" t="n">
         <v>314381</v>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B27" s="0" t="inlineStr">
         <is>
           <t>骨</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
+      <c r="C27" s="0" t="inlineStr">
         <is>
           <t>gǔ</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
+      <c r="D27" s="0" t="inlineStr">
         <is>
           <t>骨头</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
+      <c r="E27" s="0" t="inlineStr">
         <is>
           <t>gǔ tou</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="n">
+      <c r="A28" s="0" t="n">
         <v>314382</v>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B28" s="0" t="inlineStr">
         <is>
           <t>处</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
+      <c r="C28" s="0" t="inlineStr">
         <is>
           <t>chǔ</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
+      <c r="D28" s="0" t="inlineStr">
         <is>
           <t>处理</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
+      <c r="E28" s="0" t="inlineStr">
         <is>
           <t>chǔ lǐ</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="n">
+      <c r="A29" s="0" t="n">
         <v>314382</v>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="B29" s="0" t="inlineStr">
         <is>
           <t>处</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
+      <c r="C29" s="0" t="inlineStr">
         <is>
           <t>chù</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr">
+      <c r="D29" s="0" t="inlineStr">
         <is>
           <t>到处</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
+      <c r="E29" s="0" t="inlineStr">
         <is>
           <t>dào chù</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="n">
+      <c r="A30" s="0" t="n">
         <v>315181</v>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="B30" s="0" t="inlineStr">
         <is>
           <t>啦</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
+      <c r="C30" s="0" t="inlineStr">
         <is>
           <t>lā</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr"/>
-      <c r="E30" t="inlineStr"/>
+      <c r="D30" s="0" t="inlineStr"/>
+      <c r="E30" s="0" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" t="n">
+      <c r="A31" s="0" t="n">
         <v>315181</v>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="B31" s="0" t="inlineStr">
         <is>
           <t>啦</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
+      <c r="C31" s="0" t="inlineStr">
         <is>
           <t>la</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr">
+      <c r="D31" s="0" t="inlineStr">
         <is>
           <t>好啦</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
+      <c r="E31" s="0" t="inlineStr">
         <is>
           <t>hǎo la</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" t="n">
+      <c r="A32" s="0" t="n">
         <v>316181</v>
       </c>
-      <c r="B32" t="inlineStr">
+      <c r="B32" s="0" t="inlineStr">
         <is>
           <t>参</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
+      <c r="C32" s="0" t="inlineStr">
         <is>
           <t>shēn</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr">
+      <c r="D32" s="0" t="inlineStr">
         <is>
           <t>海参</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr">
+      <c r="E32" s="0" t="inlineStr">
         <is>
           <t>hǎi shēn</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="n">
+      <c r="A33" s="0" t="n">
         <v>316181</v>
       </c>
-      <c r="B33" t="inlineStr">
+      <c r="B33" s="0" t="inlineStr">
         <is>
           <t>参</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
+      <c r="C33" s="0" t="inlineStr">
         <is>
           <t>cān</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr">
+      <c r="D33" s="0" t="inlineStr">
         <is>
           <t>参加</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr">
+      <c r="E33" s="0" t="inlineStr">
         <is>
           <t>cān jiā</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" t="n">
+      <c r="A34" s="0" t="n">
         <v>316181</v>
       </c>
-      <c r="B34" t="inlineStr">
+      <c r="B34" s="0" t="inlineStr">
         <is>
           <t>参</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
+      <c r="C34" s="0" t="inlineStr">
         <is>
           <t>cēn</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr">
+      <c r="D34" s="0" t="inlineStr">
         <is>
           <t>参差不齐</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr">
+      <c r="E34" s="0" t="inlineStr">
         <is>
           <t>cēn cī bù qí</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" t="n">
+      <c r="A35" s="0" t="n">
         <v>316281</v>
       </c>
-      <c r="B35" t="inlineStr">
+      <c r="B35" s="0" t="inlineStr">
         <is>
           <t>臂</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr">
+      <c r="C35" s="0" t="inlineStr">
         <is>
           <t>bei</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr">
+      <c r="D35" s="0" t="inlineStr">
         <is>
           <t>胳臂</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr">
+      <c r="E35" s="0" t="inlineStr">
         <is>
           <t>gē bei</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" t="n">
+      <c r="A36" s="0" t="n">
         <v>316281</v>
       </c>
-      <c r="B36" t="inlineStr">
+      <c r="B36" s="0" t="inlineStr">
         <is>
           <t>臂</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr">
+      <c r="C36" s="0" t="inlineStr">
         <is>
           <t>bì</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr">
+      <c r="D36" s="0" t="inlineStr">
         <is>
           <t>臂膀</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr">
+      <c r="E36" s="0" t="inlineStr">
         <is>
           <t>bì bǎng</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" t="n">
+      <c r="A37" s="0" t="n">
         <v>316381</v>
       </c>
-      <c r="B37" t="inlineStr">
+      <c r="B37" s="0" t="inlineStr">
         <is>
           <t>兴</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
+      <c r="C37" s="0" t="inlineStr">
         <is>
           <t>xīng</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr">
+      <c r="D37" s="0" t="inlineStr">
         <is>
           <t>兴旺</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr">
+      <c r="E37" s="0" t="inlineStr">
         <is>
           <t>xīng wàng</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" t="n">
+      <c r="A38" s="0" t="n">
         <v>316381</v>
       </c>
-      <c r="B38" t="inlineStr">
+      <c r="B38" s="0" t="inlineStr">
         <is>
           <t>兴</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
+      <c r="C38" s="0" t="inlineStr">
         <is>
           <t>xìng</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr">
+      <c r="D38" s="0" t="inlineStr">
         <is>
           <t>高兴</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr">
+      <c r="E38" s="0" t="inlineStr">
         <is>
           <t>gāo xìng</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" t="n">
+      <c r="A39" s="0" t="n">
         <v>316382</v>
       </c>
-      <c r="B39" t="inlineStr">
+      <c r="B39" s="0" t="inlineStr">
         <is>
           <t>舍</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr">
+      <c r="C39" s="0" t="inlineStr">
         <is>
           <t>shè</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr">
+      <c r="D39" s="0" t="inlineStr">
         <is>
           <t>宿舍</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr">
+      <c r="E39" s="0" t="inlineStr">
         <is>
           <t>sù shè</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" t="n">
+      <c r="A40" s="0" t="n">
         <v>316382</v>
       </c>
-      <c r="B40" t="inlineStr">
+      <c r="B40" s="0" t="inlineStr">
         <is>
           <t>舍</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr">
+      <c r="C40" s="0" t="inlineStr">
         <is>
           <t>shě</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr">
+      <c r="D40" s="0" t="inlineStr">
         <is>
           <t>舍弃</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr">
+      <c r="E40" s="0" t="inlineStr">
         <is>
           <t>shě qì</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" t="n">
+      <c r="A41" s="0" t="n">
         <v>316481</v>
       </c>
-      <c r="B41" t="inlineStr">
+      <c r="B41" s="0" t="inlineStr">
         <is>
           <t>角</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
+      <c r="C41" s="0" t="inlineStr">
         <is>
           <t>jué</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr">
+      <c r="D41" s="0" t="inlineStr">
         <is>
           <t>角色</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr">
+      <c r="E41" s="0" t="inlineStr">
         <is>
           <t>jué sè</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" t="n">
+      <c r="A42" s="0" t="n">
         <v>316481</v>
       </c>
-      <c r="B42" t="inlineStr">
+      <c r="B42" s="0" t="inlineStr">
         <is>
           <t>角</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr">
+      <c r="C42" s="0" t="inlineStr">
         <is>
           <t>jiǎo</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr">
+      <c r="D42" s="0" t="inlineStr">
         <is>
           <t>墙角</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr">
+      <c r="E42" s="0" t="inlineStr">
         <is>
           <t>qiáng jiǎo</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" t="n">
+      <c r="A43" s="0" t="n">
         <v>317181</v>
       </c>
-      <c r="B43" t="inlineStr">
+      <c r="B43" s="0" t="inlineStr">
         <is>
           <t>抹</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr">
+      <c r="C43" s="0" t="inlineStr">
         <is>
           <t>mǒ</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr">
+      <c r="D43" s="0" t="inlineStr">
         <is>
           <t>涂抹</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr">
+      <c r="E43" s="0" t="inlineStr">
         <is>
           <t>tú mǒ</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" t="n">
+      <c r="A44" s="0" t="n">
         <v>317181</v>
       </c>
-      <c r="B44" t="inlineStr">
+      <c r="B44" s="0" t="inlineStr">
         <is>
           <t>抹</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr">
+      <c r="C44" s="0" t="inlineStr">
         <is>
           <t>mā</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr">
+      <c r="D44" s="0" t="inlineStr">
         <is>
           <t>抹布</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr">
+      <c r="E44" s="0" t="inlineStr">
         <is>
           <t>mā bù</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" t="n">
+      <c r="A45" s="0" t="n">
         <v>317181</v>
       </c>
-      <c r="B45" t="inlineStr">
+      <c r="B45" s="0" t="inlineStr">
         <is>
           <t>抹</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr">
+      <c r="C45" s="0" t="inlineStr">
         <is>
           <t>mò</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr">
+      <c r="D45" s="0" t="inlineStr">
         <is>
           <t>抹墙</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr">
+      <c r="E45" s="0" t="inlineStr">
         <is>
           <t>mò qiáng</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" t="n">
+      <c r="A46" s="0" t="n">
         <v>317281</v>
       </c>
-      <c r="B46" t="inlineStr">
+      <c r="B46" s="0" t="inlineStr">
         <is>
           <t>呢</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr">
+      <c r="C46" s="0" t="inlineStr">
         <is>
           <t>ní</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr">
+      <c r="D46" s="0" t="inlineStr">
         <is>
           <t>呢喃</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr">
+      <c r="E46" s="0" t="inlineStr">
         <is>
           <t>ní nán</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" t="n">
+      <c r="A47" s="0" t="n">
         <v>317281</v>
       </c>
-      <c r="B47" t="inlineStr">
+      <c r="B47" s="0" t="inlineStr">
         <is>
           <t>呢</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr">
+      <c r="C47" s="0" t="inlineStr">
         <is>
           <t>ne</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr">
+      <c r="D47" s="0" t="inlineStr">
         <is>
           <t>早着呢</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr">
+      <c r="E47" s="0" t="inlineStr">
         <is>
           <t>zǎo zhe ne</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" t="n">
+      <c r="A48" s="0" t="n">
         <v>318381</v>
       </c>
-      <c r="B48" t="inlineStr">
+      <c r="B48" s="0" t="inlineStr">
         <is>
           <t>大</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr">
+      <c r="C48" s="0" t="inlineStr">
         <is>
           <t>dài</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr">
+      <c r="D48" s="0" t="inlineStr">
         <is>
           <t>大夫</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr">
+      <c r="E48" s="0" t="inlineStr">
         <is>
           <t>dài fu</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" t="n">
+      <c r="A49" s="0" t="n">
         <v>318381</v>
       </c>
-      <c r="B49" t="inlineStr">
+      <c r="B49" s="0" t="inlineStr">
         <is>
           <t>大</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr">
+      <c r="C49" s="0" t="inlineStr">
         <is>
           <t>dà</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr">
+      <c r="D49" s="0" t="inlineStr">
         <is>
           <t>大家</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr">
+      <c r="E49" s="0" t="inlineStr">
         <is>
           <t>dà jiā</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" t="n">
+      <c r="A50" s="0" t="n">
         <v>318382</v>
       </c>
-      <c r="B50" t="inlineStr">
+      <c r="B50" s="0" t="inlineStr">
         <is>
           <t>担</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr">
+      <c r="C50" s="0" t="inlineStr">
         <is>
           <t>dān</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr">
+      <c r="D50" s="0" t="inlineStr">
         <is>
           <t>担水</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr">
+      <c r="E50" s="0" t="inlineStr">
         <is>
           <t>dān shuǐ</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" t="n">
+      <c r="A51" s="0" t="n">
         <v>318382</v>
       </c>
-      <c r="B51" t="inlineStr">
+      <c r="B51" s="0" t="inlineStr">
         <is>
           <t>担</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr">
+      <c r="C51" s="0" t="inlineStr">
         <is>
           <t>dàn</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr">
+      <c r="D51" s="0" t="inlineStr">
         <is>
           <t>重担</t>
         </is>
       </c>
-      <c r="E51" t="inlineStr">
+      <c r="E51" s="0" t="inlineStr">
         <is>
           <t>zhòng dàn</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" t="n">
+      <c r="A52" s="0" t="n">
         <v>318481</v>
       </c>
-      <c r="B52" t="inlineStr">
+      <c r="B52" s="0" t="inlineStr">
         <is>
           <t>还</t>
         </is>
       </c>
-      <c r="C52" t="inlineStr">
+      <c r="C52" s="0" t="inlineStr">
         <is>
           <t>huán</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr">
+      <c r="D52" s="0" t="inlineStr">
         <is>
           <t>还价</t>
         </is>
       </c>
-      <c r="E52" t="inlineStr">
+      <c r="E52" s="0" t="inlineStr">
         <is>
           <t>huán jià</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" t="n">
+      <c r="A53" s="0" t="n">
         <v>318481</v>
       </c>
-      <c r="B53" t="inlineStr">
+      <c r="B53" s="0" t="inlineStr">
         <is>
           <t>还</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr">
+      <c r="C53" s="0" t="inlineStr">
         <is>
           <t>hái</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr">
+      <c r="D53" s="0" t="inlineStr">
         <is>
           <t>还有</t>
         </is>
       </c>
-      <c r="E53" t="inlineStr">
+      <c r="E53" s="0" t="inlineStr">
         <is>
           <t>hái yǒu</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" t="n">
+      <c r="A54" s="0" t="n">
         <v>318482</v>
       </c>
-      <c r="B54" t="inlineStr">
+      <c r="B54" s="0" t="inlineStr">
         <is>
           <t>禁</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr">
+      <c r="C54" s="0" t="inlineStr">
         <is>
           <t>jīn</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr">
+      <c r="D54" s="0" t="inlineStr">
         <is>
           <t>情不自禁</t>
         </is>
       </c>
-      <c r="E54" t="inlineStr">
+      <c r="E54" s="0" t="inlineStr">
         <is>
           <t>qíng bù zì jīn</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" t="n">
+      <c r="A55" s="0" t="n">
         <v>318482</v>
       </c>
-      <c r="B55" t="inlineStr">
+      <c r="B55" s="0" t="inlineStr">
         <is>
           <t>禁</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr">
+      <c r="C55" s="0" t="inlineStr">
         <is>
           <t>jìn</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr">
+      <c r="D55" s="0" t="inlineStr">
         <is>
           <t>禁止</t>
         </is>
       </c>
-      <c r="E55" t="inlineStr">
+      <c r="E55" s="0" t="inlineStr">
         <is>
           <t>jìn zhǐ</t>
         </is>
@@ -6675,7 +8095,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D251"/>
+  <dimension ref="A1:D450"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.15"/>
   <cols>
     <col width="10.5" customWidth="1" style="1" min="1" max="1"/>
@@ -11705,6 +13125,2991 @@
         </is>
       </c>
     </row>
+    <row r="252">
+      <c r="A252" t="n">
+        <v>311051</v>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>搭配</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>敬爱的老师</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="n">
+        <v>311052</v>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>搭配</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>飘扬的国旗</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="n">
+        <v>311053</v>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>搭配</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>可爱的小学</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="n">
+        <v>311054</v>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>搭配</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>古老的铜钟</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="n">
+        <v>311055</v>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>搭配</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>粗壮的枝干</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="n">
+        <v>311056</v>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>搭配</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>洁白的墙</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="n">
+        <v>311057</v>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>搭配</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>吹着风笛</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="n">
+        <v>311058</v>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>搭配</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>拍着大手</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="n">
+        <v>311059</v>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>搭配</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>扬起双臂</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="n">
+        <v>311060</v>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>搭配</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>一字不漏地背</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="n">
+        <v>311061</v>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>AABB式</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>高高兴兴</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="n">
+        <v>311062</v>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>AABB式</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>明明白白</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="n">
+        <v>311063</v>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>AABB式</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>平平安安</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="n">
+        <v>311064</v>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>ABAC式</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>糊里糊涂</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="n">
+        <v>311065</v>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>ABAC式</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>绘声绘色</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="n">
+        <v>311066</v>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>ABAC式</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>人来人往</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="n">
+        <v>311067</v>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>ABAC式</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>无边无际</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="n">
+        <v>311068</v>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>ABAC式</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>多姿多彩</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="n">
+        <v>311069</v>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>一~不~式</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>一字不漏</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="n">
+        <v>311070</v>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>一~不~式</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>一丝不苟</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="n">
+        <v>311071</v>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>一~不~式</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>一文不值</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="n">
+        <v>311072</v>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>一~不~式</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>一言不发</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="n">
+        <v>311073</v>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>一~不~式</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>一成不变</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="n">
+        <v>312051</v>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>搭配</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>一排排大雁</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="n">
+        <v>312052</v>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>搭配</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>一阵阵秋风</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="n">
+        <v>312053</v>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>搭配</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>一颗谷粒</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="n">
+        <v>312054</v>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>搭配</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>一角小小的蓝天</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="n">
+        <v>312055</v>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>搭配</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>一块彩色的地毯</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="n">
+        <v>312056</v>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>搭配</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>一片片金黄金黄的叶子</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="n">
+        <v>312057</v>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>搭配</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>一个金色的小巴掌</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="n">
+        <v>312058</v>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>搭配</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>五彩缤纷的颜料</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="n">
+        <v>312059</v>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>搭配</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>金色的海洋</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="n">
+        <v>312060</v>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>搭配</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>厚厚的衣裳</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="n">
+        <v>312061</v>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>搭配</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>暖暖的叮咛</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="n">
+        <v>312062</v>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>搭配</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>丰收的歌吟</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="n">
+        <v>312063</v>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>搭配</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>饱满的谷粒</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="n">
+        <v>312064</v>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>搭配</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>辽阔透明的音乐厅</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="n">
+        <v>312065</v>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>搭配</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>抖抖手臂</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="n">
+        <v>312066</v>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>搭配</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>振动翅膀</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="n">
+        <v>312067</v>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>搭配</t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>追上白云</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="n">
+        <v>312068</v>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>搭配</t>
+        </is>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>掠过田野</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="n">
+        <v>312069</v>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>ABB式</t>
+        </is>
+      </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>湿漉漉</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="n">
+        <v>312070</v>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>ABB式</t>
+        </is>
+      </c>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>干巴巴</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="n">
+        <v>312071</v>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>ABB式</t>
+        </is>
+      </c>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>胖乎乎</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="n">
+        <v>312072</v>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>ABB式</t>
+        </is>
+      </c>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>冷冰冰</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="n">
+        <v>312073</v>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>ABB式</t>
+        </is>
+      </c>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>暖洋洋</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="n">
+        <v>312074</v>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>ABAB式</t>
+        </is>
+      </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>金黄金黄</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="n">
+        <v>312075</v>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>ABAB式</t>
+        </is>
+      </c>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>雪白雪白</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="n">
+        <v>312076</v>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>ABAB式</t>
+        </is>
+      </c>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>瓦蓝瓦蓝</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="n">
+        <v>312077</v>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>ABAB式</t>
+        </is>
+      </c>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t>火红火红</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="n">
+        <v>312078</v>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>ABAB式</t>
+        </is>
+      </c>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t>碧绿碧绿</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="n">
+        <v>312079</v>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>表示颜色多</t>
+        </is>
+      </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>五彩缤纷</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="n">
+        <v>312080</v>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>表示颜色多</t>
+        </is>
+      </c>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t>五颜六色</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="n">
+        <v>312081</v>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>表示颜色多</t>
+        </is>
+      </c>
+      <c r="C305" t="inlineStr">
+        <is>
+          <t>五光十色</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="n">
+        <v>312082</v>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>表示颜色多</t>
+        </is>
+      </c>
+      <c r="C306" t="inlineStr">
+        <is>
+          <t>万紫千红</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="n">
+        <v>313051</v>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>搭配</t>
+        </is>
+      </c>
+      <c r="C307" t="inlineStr">
+        <is>
+          <t>美丽的早晨</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="n">
+        <v>313052</v>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>搭配</t>
+        </is>
+      </c>
+      <c r="C308" t="inlineStr">
+        <is>
+          <t>舒适的小洞</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="n">
+        <v>313053</v>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>搭配</t>
+        </is>
+      </c>
+      <c r="C309" t="inlineStr">
+        <is>
+          <t>古老的橄榄树</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="n">
+        <v>313054</v>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>搭配</t>
+        </is>
+      </c>
+      <c r="C310" t="inlineStr">
+        <is>
+          <t>迷迷糊糊的思绪</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="n">
+        <v>313055</v>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>搭配</t>
+        </is>
+      </c>
+      <c r="C311" t="inlineStr">
+        <is>
+          <t>洪亮的叫声</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="n">
+        <v>313056</v>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>搭配</t>
+        </is>
+      </c>
+      <c r="C312" t="inlineStr">
+        <is>
+          <t>百发百中的神枪手</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="n">
+        <v>313057</v>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>搭配</t>
+        </is>
+      </c>
+      <c r="C313" t="inlineStr">
+        <is>
+          <t>美味可口的午餐</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="n">
+        <v>313058</v>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>搭配</t>
+        </is>
+      </c>
+      <c r="C314" t="inlineStr">
+        <is>
+          <t>友好地回答</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="n">
+        <v>313059</v>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>搭配</t>
+        </is>
+      </c>
+      <c r="C315" t="inlineStr">
+        <is>
+          <t>满怀信心地说</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="n">
+        <v>313060</v>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>搭配</t>
+        </is>
+      </c>
+      <c r="C316" t="inlineStr">
+        <is>
+          <t>日夜不停地赶路</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="n">
+        <v>313061</v>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>搭配</t>
+        </is>
+      </c>
+      <c r="C317" t="inlineStr">
+        <is>
+          <t>安详地吃草</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="n">
+        <v>313062</v>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>搭配</t>
+        </is>
+      </c>
+      <c r="C318" t="inlineStr">
+        <is>
+          <t>参加婚礼</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="n">
+        <v>313063</v>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>搭配</t>
+        </is>
+      </c>
+      <c r="C319" t="inlineStr">
+        <is>
+          <t>参加庆典</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="n">
+        <v>313064</v>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>搭配</t>
+        </is>
+      </c>
+      <c r="C320" t="inlineStr">
+        <is>
+          <t>陷入沉思</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="n">
+        <v>313065</v>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>搭配</t>
+        </is>
+      </c>
+      <c r="C321" t="inlineStr">
+        <is>
+          <t>拿定主意</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="n">
+        <v>313066</v>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>搭配</t>
+        </is>
+      </c>
+      <c r="C322" t="inlineStr">
+        <is>
+          <t>瞪着双眼</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="n">
+        <v>313067</v>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>搭配</t>
+        </is>
+      </c>
+      <c r="C323" t="inlineStr">
+        <is>
+          <t>阳光灿烂</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="n">
+        <v>313068</v>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>搭配</t>
+        </is>
+      </c>
+      <c r="C324" t="inlineStr">
+        <is>
+          <t>路途遥远</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="n">
+        <v>313069</v>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>ABAC式</t>
+        </is>
+      </c>
+      <c r="C325" t="inlineStr">
+        <is>
+          <t>自言自语</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="n">
+        <v>313070</v>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>ABAC式</t>
+        </is>
+      </c>
+      <c r="C326" t="inlineStr">
+        <is>
+          <t>有声有色</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="n">
+        <v>313071</v>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>ABAC式</t>
+        </is>
+      </c>
+      <c r="C327" t="inlineStr">
+        <is>
+          <t>有板有眼</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="n">
+        <v>313072</v>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>ABAC式</t>
+        </is>
+      </c>
+      <c r="C328" t="inlineStr">
+        <is>
+          <t>不慌不忙</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="n">
+        <v>313073</v>
+      </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>AABC式</t>
+        </is>
+      </c>
+      <c r="C329" t="inlineStr">
+        <is>
+          <t>哈哈大笑</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="n">
+        <v>313074</v>
+      </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>AABC式</t>
+        </is>
+      </c>
+      <c r="C330" t="inlineStr">
+        <is>
+          <t>欣欣向荣</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="n">
+        <v>313075</v>
+      </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>AABC式</t>
+        </is>
+      </c>
+      <c r="C331" t="inlineStr">
+        <is>
+          <t>斤斤计较</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="n">
+        <v>313076</v>
+      </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>AABC式</t>
+        </is>
+      </c>
+      <c r="C332" t="inlineStr">
+        <is>
+          <t>蒸蒸日上</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="n">
+        <v>313077</v>
+      </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>AABC式</t>
+        </is>
+      </c>
+      <c r="C333" t="inlineStr">
+        <is>
+          <t>遥遥领先</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="n">
+        <v>313078</v>
+      </c>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>AABC式</t>
+        </is>
+      </c>
+      <c r="C334" t="inlineStr">
+        <is>
+          <t>井井有条</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="n">
+        <v>313079</v>
+      </c>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>AABB式</t>
+        </is>
+      </c>
+      <c r="C335" t="inlineStr">
+        <is>
+          <t>迷迷糊糊</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="n">
+        <v>313080</v>
+      </c>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>AABB式</t>
+        </is>
+      </c>
+      <c r="C336" t="inlineStr">
+        <is>
+          <t>干干净净</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="n">
+        <v>313081</v>
+      </c>
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>AABB式</t>
+        </is>
+      </c>
+      <c r="C337" t="inlineStr">
+        <is>
+          <t>开开心心</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="n">
+        <v>313082</v>
+      </c>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>ABB式</t>
+        </is>
+      </c>
+      <c r="C338" t="inlineStr">
+        <is>
+          <t>孤零零</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="n">
+        <v>313083</v>
+      </c>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>ABB式</t>
+        </is>
+      </c>
+      <c r="C339" t="inlineStr">
+        <is>
+          <t>亮闪闪</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="n">
+        <v>313084</v>
+      </c>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>ABB式</t>
+        </is>
+      </c>
+      <c r="C340" t="inlineStr">
+        <is>
+          <t>金灿灿</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="n">
+        <v>313085</v>
+      </c>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>ABB式</t>
+        </is>
+      </c>
+      <c r="C341" t="inlineStr">
+        <is>
+          <t>香喷喷</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="n">
+        <v>313086</v>
+      </c>
+      <c r="B342" t="inlineStr">
+        <is>
+          <t>ABB式</t>
+        </is>
+      </c>
+      <c r="C342" t="inlineStr">
+        <is>
+          <t>绿油油</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="n">
+        <v>313087</v>
+      </c>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>ABB式</t>
+        </is>
+      </c>
+      <c r="C343" t="inlineStr">
+        <is>
+          <t>脆生生</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="n">
+        <v>314051</v>
+      </c>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>搭配</t>
+        </is>
+      </c>
+      <c r="C344" t="inlineStr">
+        <is>
+          <t>平平常常的普通人</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="n">
+        <v>314052</v>
+      </c>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>搭配</t>
+        </is>
+      </c>
+      <c r="C345" t="inlineStr">
+        <is>
+          <t>又瘦又长的向日葵</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="n">
+        <v>314053</v>
+      </c>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>搭配</t>
+        </is>
+      </c>
+      <c r="C346" t="inlineStr">
+        <is>
+          <t>可怜巴巴的样儿</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="n">
+        <v>314054</v>
+      </c>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>搭配</t>
+        </is>
+      </c>
+      <c r="C347" t="inlineStr">
+        <is>
+          <t>诱人的奶酪</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="n">
+        <v>314055</v>
+      </c>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>搭配</t>
+        </is>
+      </c>
+      <c r="C348" t="inlineStr">
+        <is>
+          <t>四面八方的草丛</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="n">
+        <v>314056</v>
+      </c>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>搭配</t>
+        </is>
+      </c>
+      <c r="C349" t="inlineStr">
+        <is>
+          <t>集合队伍</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="n">
+        <v>314057</v>
+      </c>
+      <c r="B350" t="inlineStr">
+        <is>
+          <t>搭配</t>
+        </is>
+      </c>
+      <c r="C350" t="inlineStr">
+        <is>
+          <t>搬运粮食</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="n">
+        <v>314058</v>
+      </c>
+      <c r="B351" t="inlineStr">
+        <is>
+          <t>搭配</t>
+        </is>
+      </c>
+      <c r="C351" t="inlineStr">
+        <is>
+          <t>登上石板</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="n">
+        <v>314059</v>
+      </c>
+      <c r="B352" t="inlineStr">
+        <is>
+          <t>搭配</t>
+        </is>
+      </c>
+      <c r="C352" t="inlineStr">
+        <is>
+          <t>争先恐后赶到</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="n">
+        <v>315051</v>
+      </c>
+      <c r="B353" t="inlineStr">
+        <is>
+          <t>搭配</t>
+        </is>
+      </c>
+      <c r="C353" t="inlineStr">
+        <is>
+          <t>翠绿的羽毛</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="n">
+        <v>315052</v>
+      </c>
+      <c r="B354" t="inlineStr">
+        <is>
+          <t>搭配</t>
+        </is>
+      </c>
+      <c r="C354" t="inlineStr">
+        <is>
+          <t>红色的长嘴</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="n">
+        <v>315053</v>
+      </c>
+      <c r="B355" t="inlineStr">
+        <is>
+          <t>搭配</t>
+        </is>
+      </c>
+      <c r="C355" t="inlineStr">
+        <is>
+          <t>金色的草地</t>
+        </is>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="n">
+        <v>315054</v>
+      </c>
+      <c r="B356" t="inlineStr">
+        <is>
+          <t>搭配</t>
+        </is>
+      </c>
+      <c r="C356" t="inlineStr">
+        <is>
+          <t>一本正经的样子</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="n">
+        <v>315055</v>
+      </c>
+      <c r="B357" t="inlineStr">
+        <is>
+          <t>搭配</t>
+        </is>
+      </c>
+      <c r="C357" t="inlineStr">
+        <is>
+          <t>披着蓑衣</t>
+        </is>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="n">
+        <v>315056</v>
+      </c>
+      <c r="B358" t="inlineStr">
+        <is>
+          <t>搭配</t>
+        </is>
+      </c>
+      <c r="C358" t="inlineStr">
+        <is>
+          <t>冲进水里</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="n">
+        <v>315057</v>
+      </c>
+      <c r="B359" t="inlineStr">
+        <is>
+          <t>搭配</t>
+        </is>
+      </c>
+      <c r="C359" t="inlineStr">
+        <is>
+          <t>衔着小鱼</t>
+        </is>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="n">
+        <v>315058</v>
+      </c>
+      <c r="B360" t="inlineStr">
+        <is>
+          <t>搭配</t>
+        </is>
+      </c>
+      <c r="C360" t="inlineStr">
+        <is>
+          <t>打哈欠</t>
+        </is>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="n">
+        <v>315059</v>
+      </c>
+      <c r="B361" t="inlineStr">
+        <is>
+          <t>搭配</t>
+        </is>
+      </c>
+      <c r="C361" t="inlineStr">
+        <is>
+          <t>沙啦沙啦地响</t>
+        </is>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="n">
+        <v>315060</v>
+      </c>
+      <c r="B362" t="inlineStr">
+        <is>
+          <t>搭配</t>
+        </is>
+      </c>
+      <c r="C362" t="inlineStr">
+        <is>
+          <t>用力地摇着橹</t>
+        </is>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="n">
+        <v>315061</v>
+      </c>
+      <c r="B363" t="inlineStr">
+        <is>
+          <t>搭配</t>
+        </is>
+      </c>
+      <c r="C363" t="inlineStr">
+        <is>
+          <t>静悄悄地停在船头</t>
+        </is>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="n">
+        <v>315062</v>
+      </c>
+      <c r="B364" t="inlineStr">
+        <is>
+          <t>ABB式</t>
+        </is>
+      </c>
+      <c r="C364" t="inlineStr">
+        <is>
+          <t>闹哄哄</t>
+        </is>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="n">
+        <v>315063</v>
+      </c>
+      <c r="B365" t="inlineStr">
+        <is>
+          <t>ABB式</t>
+        </is>
+      </c>
+      <c r="C365" t="inlineStr">
+        <is>
+          <t>哗啦啦</t>
+        </is>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="n">
+        <v>315064</v>
+      </c>
+      <c r="B366" t="inlineStr">
+        <is>
+          <t>ABB式</t>
+        </is>
+      </c>
+      <c r="C366" t="inlineStr">
+        <is>
+          <t>呼啦啦</t>
+        </is>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="n">
+        <v>315065</v>
+      </c>
+      <c r="B367" t="inlineStr">
+        <is>
+          <t>ABB式</t>
+        </is>
+      </c>
+      <c r="C367" t="inlineStr">
+        <is>
+          <t>轰隆隆</t>
+        </is>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="n">
+        <v>315066</v>
+      </c>
+      <c r="B368" t="inlineStr">
+        <is>
+          <t>含目的成语</t>
+        </is>
+      </c>
+      <c r="C368" t="inlineStr">
+        <is>
+          <t>引人注目</t>
+        </is>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="n">
+        <v>315067</v>
+      </c>
+      <c r="B369" t="inlineStr">
+        <is>
+          <t>含目的成语</t>
+        </is>
+      </c>
+      <c r="C369" t="inlineStr">
+        <is>
+          <t>目不转睛</t>
+        </is>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="n">
+        <v>315068</v>
+      </c>
+      <c r="B370" t="inlineStr">
+        <is>
+          <t>含目的成语</t>
+        </is>
+      </c>
+      <c r="C370" t="inlineStr">
+        <is>
+          <t>光彩夺目</t>
+        </is>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="n">
+        <v>315069</v>
+      </c>
+      <c r="B371" t="inlineStr">
+        <is>
+          <t>含目的成语</t>
+        </is>
+      </c>
+      <c r="C371" t="inlineStr">
+        <is>
+          <t>刮目相看</t>
+        </is>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="n">
+        <v>316051</v>
+      </c>
+      <c r="B372" t="inlineStr">
+        <is>
+          <t>搭配</t>
+        </is>
+      </c>
+      <c r="C372" t="inlineStr">
+        <is>
+          <t>绽开的花朵</t>
+        </is>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="n">
+        <v>316052</v>
+      </c>
+      <c r="B373" t="inlineStr">
+        <is>
+          <t>搭配</t>
+        </is>
+      </c>
+      <c r="C373" t="inlineStr">
+        <is>
+          <t>青色的虾</t>
+        </is>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="n">
+        <v>316053</v>
+      </c>
+      <c r="B374" t="inlineStr">
+        <is>
+          <t>搭配</t>
+        </is>
+      </c>
+      <c r="C374" t="inlineStr">
+        <is>
+          <t>茂密的树林</t>
+        </is>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="n">
+        <v>316054</v>
+      </c>
+      <c r="B375" t="inlineStr">
+        <is>
+          <t>搭配</t>
+        </is>
+      </c>
+      <c r="C375" t="inlineStr">
+        <is>
+          <t>各种各样的珊瑚</t>
+        </is>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="n">
+        <v>316055</v>
+      </c>
+      <c r="B376" t="inlineStr">
+        <is>
+          <t>搭配</t>
+        </is>
+      </c>
+      <c r="C376" t="inlineStr">
+        <is>
+          <t>彩色的条纹</t>
+        </is>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="n">
+        <v>316056</v>
+      </c>
+      <c r="B377" t="inlineStr">
+        <is>
+          <t>搭配</t>
+        </is>
+      </c>
+      <c r="C377" t="inlineStr">
+        <is>
+          <t>浩瀚的大海</t>
+        </is>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="n">
+        <v>316057</v>
+      </c>
+      <c r="B378" t="inlineStr">
+        <is>
+          <t>搭配</t>
+        </is>
+      </c>
+      <c r="C378" t="inlineStr">
+        <is>
+          <t>棕色的机帆船</t>
+        </is>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="n">
+        <v>316058</v>
+      </c>
+      <c r="B379" t="inlineStr">
+        <is>
+          <t>搭配</t>
+        </is>
+      </c>
+      <c r="C379" t="inlineStr">
+        <is>
+          <t>银色的军舰</t>
+        </is>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="n">
+        <v>316059</v>
+      </c>
+      <c r="B380" t="inlineStr">
+        <is>
+          <t>搭配</t>
+        </is>
+      </c>
+      <c r="C380" t="inlineStr">
+        <is>
+          <t>白色的海鸥</t>
+        </is>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="n">
+        <v>316060</v>
+      </c>
+      <c r="B381" t="inlineStr">
+        <is>
+          <t>搭配</t>
+        </is>
+      </c>
+      <c r="C381" t="inlineStr">
+        <is>
+          <t>金黄色的海螺</t>
+        </is>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="n">
+        <v>316061</v>
+      </c>
+      <c r="B382" t="inlineStr">
+        <is>
+          <t>搭配</t>
+        </is>
+      </c>
+      <c r="C382" t="inlineStr">
+        <is>
+          <t>银光闪闪的鱼</t>
+        </is>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="n">
+        <v>316062</v>
+      </c>
+      <c r="B383" t="inlineStr">
+        <is>
+          <t>搭配</t>
+        </is>
+      </c>
+      <c r="C383" t="inlineStr">
+        <is>
+          <t>绿色的海洋</t>
+        </is>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="n">
+        <v>316063</v>
+      </c>
+      <c r="B384" t="inlineStr">
+        <is>
+          <t>搭配</t>
+        </is>
+      </c>
+      <c r="C384" t="inlineStr">
+        <is>
+          <t>嫩绿的叶子</t>
+        </is>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="n">
+        <v>316064</v>
+      </c>
+      <c r="B385" t="inlineStr">
+        <is>
+          <t>搭配</t>
+        </is>
+      </c>
+      <c r="C385" t="inlineStr">
+        <is>
+          <t>巨大的宝库</t>
+        </is>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="n">
+        <v>316065</v>
+      </c>
+      <c r="B386" t="inlineStr">
+        <is>
+          <t>搭配</t>
+        </is>
+      </c>
+      <c r="C386" t="inlineStr">
+        <is>
+          <t>乳白色的浓雾</t>
+        </is>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="n">
+        <v>316066</v>
+      </c>
+      <c r="B387" t="inlineStr">
+        <is>
+          <t>搭配</t>
+        </is>
+      </c>
+      <c r="C387" t="inlineStr">
+        <is>
+          <t>密密层层的枝叶</t>
+        </is>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="n">
+        <v>316067</v>
+      </c>
+      <c r="B388" t="inlineStr">
+        <is>
+          <t>搭配</t>
+        </is>
+      </c>
+      <c r="C388" t="inlineStr">
+        <is>
+          <t>鲜嫩的蘑菇</t>
+        </is>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="n">
+        <v>316068</v>
+      </c>
+      <c r="B389" t="inlineStr">
+        <is>
+          <t>搭配</t>
+        </is>
+      </c>
+      <c r="C389" t="inlineStr">
+        <is>
+          <t>多元的文化</t>
+        </is>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="n">
+        <v>316069</v>
+      </c>
+      <c r="B390" t="inlineStr">
+        <is>
+          <t>搭配</t>
+        </is>
+      </c>
+      <c r="C390" t="inlineStr">
+        <is>
+          <t>闪烁的灯光</t>
+        </is>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="n">
+        <v>316070</v>
+      </c>
+      <c r="B391" t="inlineStr">
+        <is>
+          <t>搭配</t>
+        </is>
+      </c>
+      <c r="C391" t="inlineStr">
+        <is>
+          <t>绚丽多姿的夜景</t>
+        </is>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="n">
+        <v>316071</v>
+      </c>
+      <c r="B392" t="inlineStr">
+        <is>
+          <t>搭配</t>
+        </is>
+      </c>
+      <c r="C392" t="inlineStr">
+        <is>
+          <t>五颜六色的焰火</t>
+        </is>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="n">
+        <v>316072</v>
+      </c>
+      <c r="B393" t="inlineStr">
+        <is>
+          <t>搭配</t>
+        </is>
+      </c>
+      <c r="C393" t="inlineStr">
+        <is>
+          <t>奔流不息的长河</t>
+        </is>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="n">
+        <v>316073</v>
+      </c>
+      <c r="B394" t="inlineStr">
+        <is>
+          <t>搭配</t>
+        </is>
+      </c>
+      <c r="C394" t="inlineStr">
+        <is>
+          <t>流光溢彩的霓虹灯</t>
+        </is>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="n">
+        <v>316074</v>
+      </c>
+      <c r="B395" t="inlineStr">
+        <is>
+          <t>搭配</t>
+        </is>
+      </c>
+      <c r="C395" t="inlineStr">
+        <is>
+          <t>璀璨夺目的明珠</t>
+        </is>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="n">
+        <v>316075</v>
+      </c>
+      <c r="B396" t="inlineStr">
+        <is>
+          <t>搭配</t>
+        </is>
+      </c>
+      <c r="C396" t="inlineStr">
+        <is>
+          <t>淙淙地流着</t>
+        </is>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="n">
+        <v>316076</v>
+      </c>
+      <c r="B397" t="inlineStr">
+        <is>
+          <t>搭配</t>
+        </is>
+      </c>
+      <c r="C397" t="inlineStr">
+        <is>
+          <t>呼呼地刮过</t>
+        </is>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="n">
+        <v>316077</v>
+      </c>
+      <c r="B398" t="inlineStr">
+        <is>
+          <t>搭配</t>
+        </is>
+      </c>
+      <c r="C398" t="inlineStr">
+        <is>
+          <t>懒洋洋地蠕动</t>
+        </is>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="n">
+        <v>316078</v>
+      </c>
+      <c r="B399" t="inlineStr">
+        <is>
+          <t>搭配</t>
+        </is>
+      </c>
+      <c r="C399" t="inlineStr">
+        <is>
+          <t>风景优美</t>
+        </is>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="n">
+        <v>316079</v>
+      </c>
+      <c r="B400" t="inlineStr">
+        <is>
+          <t>搭配</t>
+        </is>
+      </c>
+      <c r="C400" t="inlineStr">
+        <is>
+          <t>物产丰饶</t>
+        </is>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="n">
+        <v>317051</v>
+      </c>
+      <c r="B401" t="inlineStr">
+        <is>
+          <t>搭配</t>
+        </is>
+      </c>
+      <c r="C401" t="inlineStr">
+        <is>
+          <t>雄伟的乐曲</t>
+        </is>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="n">
+        <v>317052</v>
+      </c>
+      <c r="B402" t="inlineStr">
+        <is>
+          <t>搭配</t>
+        </is>
+      </c>
+      <c r="C402" t="inlineStr">
+        <is>
+          <t>高远的天空</t>
+        </is>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="n">
+        <v>317053</v>
+      </c>
+      <c r="B403" t="inlineStr">
+        <is>
+          <t>搭配</t>
+        </is>
+      </c>
+      <c r="C403" t="inlineStr">
+        <is>
+          <t>广阔的大地</t>
+        </is>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="n">
+        <v>317054</v>
+      </c>
+      <c r="B404" t="inlineStr">
+        <is>
+          <t>搭配</t>
+        </is>
+      </c>
+      <c r="C404" t="inlineStr">
+        <is>
+          <t>温柔的细语</t>
+        </is>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="n">
+        <v>317055</v>
+      </c>
+      <c r="B405" t="inlineStr">
+        <is>
+          <t>搭配</t>
+        </is>
+      </c>
+      <c r="C405" t="inlineStr">
+        <is>
+          <t>无穷的奥秘</t>
+        </is>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="n">
+        <v>317056</v>
+      </c>
+      <c r="B406" t="inlineStr">
+        <is>
+          <t>搭配</t>
+        </is>
+      </c>
+      <c r="C406" t="inlineStr">
+        <is>
+          <t>无尽的乐趣</t>
+        </is>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="n">
+        <v>317057</v>
+      </c>
+      <c r="B407" t="inlineStr">
+        <is>
+          <t>搭配</t>
+        </is>
+      </c>
+      <c r="C407" t="inlineStr">
+        <is>
+          <t>热闹的音乐会</t>
+        </is>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="n">
+        <v>317058</v>
+      </c>
+      <c r="B408" t="inlineStr">
+        <is>
+          <t>搭配</t>
+        </is>
+      </c>
+      <c r="C408" t="inlineStr">
+        <is>
+          <t>沙沙的竹叶声</t>
+        </is>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="n">
+        <v>317059</v>
+      </c>
+      <c r="B409" t="inlineStr">
+        <is>
+          <t>搭配</t>
+        </is>
+      </c>
+      <c r="C409" t="inlineStr">
+        <is>
+          <t>轻轻柔柔的呢喃细语</t>
+        </is>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" t="n">
+        <v>317060</v>
+      </c>
+      <c r="B410" t="inlineStr">
+        <is>
+          <t>搭配</t>
+        </is>
+      </c>
+      <c r="C410" t="inlineStr">
+        <is>
+          <t>轻快的山中小曲</t>
+        </is>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="n">
+        <v>317061</v>
+      </c>
+      <c r="B411" t="inlineStr">
+        <is>
+          <t>搭配</t>
+        </is>
+      </c>
+      <c r="C411" t="inlineStr">
+        <is>
+          <t>波澜壮阔的海洋大合唱</t>
+        </is>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" t="n">
+        <v>317062</v>
+      </c>
+      <c r="B412" t="inlineStr">
+        <is>
+          <t>搭配</t>
+        </is>
+      </c>
+      <c r="C412" t="inlineStr">
+        <is>
+          <t>叽叽喳喳的鸟叫</t>
+        </is>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="n">
+        <v>317063</v>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>拟声词</t>
+        </is>
+      </c>
+      <c r="C413" t="inlineStr">
+        <is>
+          <t>呢喃</t>
+        </is>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="n">
+        <v>317064</v>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>拟声词</t>
+        </is>
+      </c>
+      <c r="C414" t="inlineStr">
+        <is>
+          <t>淙淙</t>
+        </is>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="n">
+        <v>317065</v>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>拟声词</t>
+        </is>
+      </c>
+      <c r="C415" t="inlineStr">
+        <is>
+          <t>潺潺</t>
+        </is>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="n">
+        <v>317066</v>
+      </c>
+      <c r="B416" t="inlineStr">
+        <is>
+          <t>拟声词</t>
+        </is>
+      </c>
+      <c r="C416" t="inlineStr">
+        <is>
+          <t>哗哗</t>
+        </is>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" t="n">
+        <v>317067</v>
+      </c>
+      <c r="B417" t="inlineStr">
+        <is>
+          <t>拟声词</t>
+        </is>
+      </c>
+      <c r="C417" t="inlineStr">
+        <is>
+          <t>叽叽喳喳</t>
+        </is>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" t="n">
+        <v>317068</v>
+      </c>
+      <c r="B418" t="inlineStr">
+        <is>
+          <t>拟声词</t>
+        </is>
+      </c>
+      <c r="C418" t="inlineStr">
+        <is>
+          <t>滴滴答答</t>
+        </is>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" t="n">
+        <v>317069</v>
+      </c>
+      <c r="B419" t="inlineStr">
+        <is>
+          <t>拟声词</t>
+        </is>
+      </c>
+      <c r="C419" t="inlineStr">
+        <is>
+          <t>叮叮咚咚</t>
+        </is>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" t="n">
+        <v>317070</v>
+      </c>
+      <c r="B420" t="inlineStr">
+        <is>
+          <t>拟声词</t>
+        </is>
+      </c>
+      <c r="C420" t="inlineStr">
+        <is>
+          <t>淅淅沥沥</t>
+        </is>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="n">
+        <v>317071</v>
+      </c>
+      <c r="B421" t="inlineStr">
+        <is>
+          <t>描写大海</t>
+        </is>
+      </c>
+      <c r="C421" t="inlineStr">
+        <is>
+          <t>波澜壮阔</t>
+        </is>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" t="n">
+        <v>317072</v>
+      </c>
+      <c r="B422" t="inlineStr">
+        <is>
+          <t>描写大海</t>
+        </is>
+      </c>
+      <c r="C422" t="inlineStr">
+        <is>
+          <t>汹涌澎湃</t>
+        </is>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" t="n">
+        <v>317073</v>
+      </c>
+      <c r="B423" t="inlineStr">
+        <is>
+          <t>描写大海</t>
+        </is>
+      </c>
+      <c r="C423" t="inlineStr">
+        <is>
+          <t>惊涛骇浪</t>
+        </is>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" t="n">
+        <v>317074</v>
+      </c>
+      <c r="B424" t="inlineStr">
+        <is>
+          <t>描写大海</t>
+        </is>
+      </c>
+      <c r="C424" t="inlineStr">
+        <is>
+          <t>滔天巨浪</t>
+        </is>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" t="n">
+        <v>317075</v>
+      </c>
+      <c r="B425" t="inlineStr">
+        <is>
+          <t>描写大海</t>
+        </is>
+      </c>
+      <c r="C425" t="inlineStr">
+        <is>
+          <t>风平浪静</t>
+        </is>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" t="n">
+        <v>317076</v>
+      </c>
+      <c r="B426" t="inlineStr">
+        <is>
+          <t>AABB式</t>
+        </is>
+      </c>
+      <c r="C426" t="inlineStr">
+        <is>
+          <t>蹦蹦跳跳</t>
+        </is>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" t="n">
+        <v>317077</v>
+      </c>
+      <c r="B427" t="inlineStr">
+        <is>
+          <t>AABB式</t>
+        </is>
+      </c>
+      <c r="C427" t="inlineStr">
+        <is>
+          <t>摇摇晃晃</t>
+        </is>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" t="n">
+        <v>317078</v>
+      </c>
+      <c r="B428" t="inlineStr">
+        <is>
+          <t>AABB式</t>
+        </is>
+      </c>
+      <c r="C428" t="inlineStr">
+        <is>
+          <t>隐隐约约</t>
+        </is>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" t="n">
+        <v>317079</v>
+      </c>
+      <c r="B429" t="inlineStr">
+        <is>
+          <t>千~百~式</t>
+        </is>
+      </c>
+      <c r="C429" t="inlineStr">
+        <is>
+          <t>千方百计</t>
+        </is>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" t="n">
+        <v>317080</v>
+      </c>
+      <c r="B430" t="inlineStr">
+        <is>
+          <t>千~百~式</t>
+        </is>
+      </c>
+      <c r="C430" t="inlineStr">
+        <is>
+          <t>千锤百炼</t>
+        </is>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" t="n">
+        <v>317081</v>
+      </c>
+      <c r="B431" t="inlineStr">
+        <is>
+          <t>千~百~式</t>
+        </is>
+      </c>
+      <c r="C431" t="inlineStr">
+        <is>
+          <t>千奇百怪</t>
+        </is>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" t="n">
+        <v>317082</v>
+      </c>
+      <c r="B432" t="inlineStr">
+        <is>
+          <t>千~百~式</t>
+        </is>
+      </c>
+      <c r="C432" t="inlineStr">
+        <is>
+          <t>千依百顺</t>
+        </is>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" t="n">
+        <v>318051</v>
+      </c>
+      <c r="B433" t="inlineStr">
+        <is>
+          <t>搭配</t>
+        </is>
+      </c>
+      <c r="C433" t="inlineStr">
+        <is>
+          <t>著名的生物学家</t>
+        </is>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" t="n">
+        <v>318052</v>
+      </c>
+      <c r="B434" t="inlineStr">
+        <is>
+          <t>搭配</t>
+        </is>
+      </c>
+      <c r="C434" t="inlineStr">
+        <is>
+          <t>卓著的成就</t>
+        </is>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" t="n">
+        <v>318053</v>
+      </c>
+      <c r="B435" t="inlineStr">
+        <is>
+          <t>搭配</t>
+        </is>
+      </c>
+      <c r="C435" t="inlineStr">
+        <is>
+          <t>偏僻的山村</t>
+        </is>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" t="n">
+        <v>318054</v>
+      </c>
+      <c r="B436" t="inlineStr">
+        <is>
+          <t>搭配</t>
+        </is>
+      </c>
+      <c r="C436" t="inlineStr">
+        <is>
+          <t>难得的学习机会</t>
+        </is>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" t="n">
+        <v>318055</v>
+      </c>
+      <c r="B437" t="inlineStr">
+        <is>
+          <t>搭配</t>
+        </is>
+      </c>
+      <c r="C437" t="inlineStr">
+        <is>
+          <t>熟练的技巧</t>
+        </is>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" t="n">
+        <v>318056</v>
+      </c>
+      <c r="B438" t="inlineStr">
+        <is>
+          <t>搭配</t>
+        </is>
+      </c>
+      <c r="C438" t="inlineStr">
+        <is>
+          <t>令人感动的故事</t>
+        </is>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" t="n">
+        <v>318057</v>
+      </c>
+      <c r="B439" t="inlineStr">
+        <is>
+          <t>搭配</t>
+        </is>
+      </c>
+      <c r="C439" t="inlineStr">
+        <is>
+          <t>鼓鼓的挂包</t>
+        </is>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" t="n">
+        <v>318058</v>
+      </c>
+      <c r="B440" t="inlineStr">
+        <is>
+          <t>搭配</t>
+        </is>
+      </c>
+      <c r="C440" t="inlineStr">
+        <is>
+          <t>敏捷地取出</t>
+        </is>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" t="n">
+        <v>318059</v>
+      </c>
+      <c r="B441" t="inlineStr">
+        <is>
+          <t>搭配</t>
+        </is>
+      </c>
+      <c r="C441" t="inlineStr">
+        <is>
+          <t>争分夺秒地做手术</t>
+        </is>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" t="n">
+        <v>318060</v>
+      </c>
+      <c r="B442" t="inlineStr">
+        <is>
+          <t>搭配</t>
+        </is>
+      </c>
+      <c r="C442" t="inlineStr">
+        <is>
+          <t>冒着危险</t>
+        </is>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" t="n">
+        <v>318061</v>
+      </c>
+      <c r="B443" t="inlineStr">
+        <is>
+          <t>搭配</t>
+        </is>
+      </c>
+      <c r="C443" t="inlineStr">
+        <is>
+          <t>含着泪花</t>
+        </is>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" t="n">
+        <v>318062</v>
+      </c>
+      <c r="B444" t="inlineStr">
+        <is>
+          <t>不~不~式</t>
+        </is>
+      </c>
+      <c r="C444" t="inlineStr">
+        <is>
+          <t>不声不响</t>
+        </is>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" t="n">
+        <v>318063</v>
+      </c>
+      <c r="B445" t="inlineStr">
+        <is>
+          <t>不~不~式</t>
+        </is>
+      </c>
+      <c r="C445" t="inlineStr">
+        <is>
+          <t>不闻不问</t>
+        </is>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" t="n">
+        <v>318064</v>
+      </c>
+      <c r="B446" t="inlineStr">
+        <is>
+          <t>不~不~式</t>
+        </is>
+      </c>
+      <c r="C446" t="inlineStr">
+        <is>
+          <t>不折不扣</t>
+        </is>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" t="n">
+        <v>318065</v>
+      </c>
+      <c r="B447" t="inlineStr">
+        <is>
+          <t>表示时间紧急</t>
+        </is>
+      </c>
+      <c r="C447" t="inlineStr">
+        <is>
+          <t>迫在眉睫</t>
+        </is>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" t="n">
+        <v>318066</v>
+      </c>
+      <c r="B448" t="inlineStr">
+        <is>
+          <t>表示时间紧急</t>
+        </is>
+      </c>
+      <c r="C448" t="inlineStr">
+        <is>
+          <t>十万火急</t>
+        </is>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" t="n">
+        <v>318067</v>
+      </c>
+      <c r="B449" t="inlineStr">
+        <is>
+          <t>表示时间紧急</t>
+        </is>
+      </c>
+      <c r="C449" t="inlineStr">
+        <is>
+          <t>火烧眉毛</t>
+        </is>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" t="n">
+        <v>318068</v>
+      </c>
+      <c r="B450" t="inlineStr">
+        <is>
+          <t>表示时间紧急</t>
+        </is>
+      </c>
+      <c r="C450" t="inlineStr">
+        <is>
+          <t>箭在弦上</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9"/>
